--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run10/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.7167,0.0186,0.0758,0.1667</t>
-  </si>
-  <si>
-    <t>0.0034,0.0075,0.0029,0.9966</t>
-  </si>
-  <si>
-    <t>0.0457,0.0396,0.0080,0.9712</t>
-  </si>
-  <si>
-    <t>0.0259,0.0098,0.0082,0.9839</t>
-  </si>
-  <si>
-    <t>0.9940,0.0018,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.9849,0.0017,0.0004,0.0095</t>
-  </si>
-  <si>
-    <t>0.9859,0.0041,0.0006,0.0055</t>
-  </si>
-  <si>
-    <t>0.9932,0.0021,0.0004,0.0019</t>
-  </si>
-  <si>
-    <t>0.9960,0.0007,0.0001,0.0016</t>
-  </si>
-  <si>
-    <t>0.9918,0.0032,0.0007,0.0023</t>
-  </si>
-  <si>
-    <t>0.9934,0.0030,0.0004,0.0017</t>
-  </si>
-  <si>
-    <t>0.9937,0.0008,0.0001,0.0038</t>
-  </si>
-  <si>
-    <t>0.6486,0.0837,0.2861,0.0165</t>
-  </si>
-  <si>
-    <t>0.0281,0.0164,0.9748,0.0010</t>
-  </si>
-  <si>
-    <t>0.0857,0.0121,0.9395,0.0030</t>
-  </si>
-  <si>
-    <t>0.2114,0.0325,0.8212,0.0059</t>
-  </si>
-  <si>
-    <t>0.2284,0.0099,0.7962,0.0236</t>
-  </si>
-  <si>
-    <t>0.0021,0.9942,0.0070,0.0007</t>
-  </si>
-  <si>
-    <t>0.0121,0.9805,0.0213,0.0016</t>
-  </si>
-  <si>
-    <t>0.2340,0.7656,0.0566,0.0030</t>
-  </si>
-  <si>
-    <t>0.0230,0.9679,0.0086,0.0024</t>
-  </si>
-  <si>
-    <t>0.0026,0.9939,0.0128,0.0003</t>
-  </si>
-  <si>
-    <t>0.3642,0.0062,0.5266,0.0534</t>
-  </si>
-  <si>
-    <t>0.2989,0.0046,0.4866,0.1154</t>
-  </si>
-  <si>
-    <t>0.0088,0.0021,0.9852,0.0080</t>
-  </si>
-  <si>
-    <t>0.1661,0.0242,0.8708,0.0073</t>
-  </si>
-  <si>
-    <t>0.0633,0.0112,0.9365,0.0099</t>
-  </si>
-  <si>
-    <t>0.0132,0.0067,0.9758,0.0080</t>
-  </si>
-  <si>
-    <t>0.0041,0.0131,0.9816,0.0162</t>
-  </si>
-  <si>
-    <t>0.4546,0.5706,0.0342,0.0077</t>
-  </si>
-  <si>
-    <t>0.1078,0.0561,0.8958,0.0035</t>
-  </si>
-  <si>
-    <t>0.0024,0.0040,0.9933,0.0045</t>
-  </si>
-  <si>
-    <t>0.0235,0.5600,0.7914,0.0020</t>
-  </si>
-  <si>
-    <t>0.7185,0.2330,0.0937,0.0277</t>
-  </si>
-  <si>
-    <t>0.1207,0.0363,0.8976,0.0089</t>
-  </si>
-  <si>
-    <t>0.6988,0.3751,0.0149,0.0036</t>
-  </si>
-  <si>
-    <t>0.0532,0.9010,0.1143,0.0122</t>
-  </si>
-  <si>
-    <t>0.0162,0.8672,0.4022,0.0220</t>
-  </si>
-  <si>
-    <t>0.0749,0.1529,0.8728,0.0073</t>
-  </si>
-  <si>
-    <t>0.0498,0.0293,0.9141,0.0280</t>
-  </si>
-  <si>
-    <t>0.0522,0.0188,0.8359,0.1395</t>
-  </si>
-  <si>
-    <t>0.0239,0.0474,0.9658,0.0021</t>
-  </si>
-  <si>
-    <t>0.0103,0.9408,0.1345,0.0097</t>
-  </si>
-  <si>
-    <t>0.0071,0.2047,0.9652,0.0046</t>
-  </si>
-  <si>
-    <t>0.0221,0.6249,0.0134,0.9058</t>
-  </si>
-  <si>
-    <t>0.0011,0.9902,0.0062,0.0266</t>
-  </si>
-  <si>
-    <t>0.0124,0.9567,0.1146,0.0043</t>
-  </si>
-  <si>
-    <t>0.0016,0.9924,0.0215,0.0028</t>
-  </si>
-  <si>
-    <t>0.0007,0.1214,0.9916,0.0006</t>
-  </si>
-  <si>
-    <t>0.0040,0.7822,0.8893,0.0014</t>
-  </si>
-  <si>
-    <t>0.0344,0.0152,0.9307,0.0473</t>
-  </si>
-  <si>
-    <t>0.0065,0.0016,0.9895,0.0044</t>
-  </si>
-  <si>
-    <t>0.0014,0.0096,0.9949,0.0026</t>
-  </si>
-  <si>
-    <t>0.0018,0.0178,0.9912,0.0031</t>
-  </si>
-  <si>
-    <t>0.9456,0.0534,0.0088,0.0066</t>
-  </si>
-  <si>
-    <t>0.9860,0.0061,0.0020,0.0033</t>
-  </si>
-  <si>
-    <t>0.9928,0.0007,0.0001,0.0045</t>
-  </si>
-  <si>
-    <t>0.0016,0.0291,0.9941,0.0013</t>
-  </si>
-  <si>
-    <t>0.9788,0.0016,0.0006,0.0140</t>
-  </si>
-  <si>
-    <t>0.9894,0.0044,0.0007,0.0028</t>
-  </si>
-  <si>
-    <t>0.9861,0.0061,0.0010,0.0037</t>
-  </si>
-  <si>
-    <t>0.0038,0.7018,0.9227,0.0024</t>
-  </si>
-  <si>
-    <t>0.0174,0.0461,0.9487,0.0232</t>
-  </si>
-  <si>
-    <t>0.0109,0.0169,0.9801,0.0042</t>
-  </si>
-  <si>
-    <t>0.0007,0.8133,0.9648,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0014,0.9984,0.0019</t>
-  </si>
-  <si>
-    <t>0.0087,0.9783,0.0387,0.0017</t>
-  </si>
-  <si>
-    <t>0.0037,0.9871,0.0268,0.0015</t>
-  </si>
-  <si>
-    <t>0.7851,0.0157,0.2334,0.0119</t>
-  </si>
-  <si>
-    <t>0.3899,0.6046,0.1036,0.0321</t>
-  </si>
-  <si>
-    <t>0.0049,0.0407,0.9874,0.0014</t>
-  </si>
-  <si>
-    <t>0.0024,0.8878,0.8324,0.0012</t>
-  </si>
-  <si>
-    <t>0.0212,0.5505,0.8434,0.0044</t>
-  </si>
-  <si>
-    <t>0.0060,0.7760,0.8343,0.0024</t>
-  </si>
-  <si>
-    <t>0.0023,0.9293,0.7815,0.0011</t>
-  </si>
-  <si>
-    <t>0.0249,0.0011,0.0197,0.9683</t>
-  </si>
-  <si>
-    <t>0.0033,0.0025,0.0015,0.9973</t>
-  </si>
-  <si>
-    <t>0.0014,0.0017,0.0009,0.9987</t>
-  </si>
-  <si>
-    <t>0.0124,0.0111,0.0073,0.9893</t>
-  </si>
-  <si>
-    <t>0.0287,0.0036,0.0096,0.9806</t>
-  </si>
-  <si>
-    <t>0.0050,0.0020,0.0061,0.9938</t>
-  </si>
-  <si>
-    <t>0.0019,0.9369,0.7623,0.0011</t>
-  </si>
-  <si>
-    <t>0.0014,0.3053,0.9864,0.0005</t>
-  </si>
-  <si>
-    <t>0.0142,0.1626,0.9599,0.0013</t>
-  </si>
-  <si>
-    <t>0.0052,0.3681,0.9649,0.0016</t>
-  </si>
-  <si>
-    <t>0.0006,0.9517,0.8710,0.0001</t>
-  </si>
-  <si>
-    <t>0.0046,0.8307,0.7884,0.0022</t>
-  </si>
-  <si>
-    <t>0.9833,0.0097,0.0014,0.0035</t>
-  </si>
-  <si>
-    <t>0.9930,0.0011,0.0001,0.0031</t>
-  </si>
-  <si>
-    <t>0.9877,0.0053,0.0005,0.0037</t>
-  </si>
-  <si>
-    <t>0.9881,0.0045,0.0008,0.0038</t>
-  </si>
-  <si>
-    <t>0.9911,0.0045,0.0003,0.0020</t>
-  </si>
-  <si>
-    <t>0.9945,0.0014,0.0002,0.0016</t>
-  </si>
-  <si>
-    <t>0.9915,0.0021,0.0004,0.0033</t>
-  </si>
-  <si>
-    <t>0.9888,0.0032,0.0004,0.0041</t>
-  </si>
-  <si>
-    <t>0.9918,0.0017,0.0004,0.0036</t>
-  </si>
-  <si>
-    <t>0.9958,0.0010,0.0002,0.0013</t>
-  </si>
-  <si>
-    <t>0.9919,0.0012,0.0002,0.0040</t>
-  </si>
-  <si>
-    <t>0.9947,0.0008,0.0002,0.0025</t>
-  </si>
-  <si>
-    <t>0.9929,0.0005,0.0001,0.0048</t>
-  </si>
-  <si>
-    <t>0.9887,0.0013,0.0002,0.0058</t>
-  </si>
-  <si>
-    <t>0.9948,0.0007,0.0002,0.0028</t>
-  </si>
-  <si>
-    <t>0.9927,0.0014,0.0003,0.0030</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9969,0.0073</t>
-  </si>
-  <si>
-    <t>0.2459,0.0303,0.7860,0.0054</t>
-  </si>
-  <si>
-    <t>0.4058,0.0859,0.4601,0.1782</t>
-  </si>
-  <si>
-    <t>0.1520,0.0077,0.8818,0.0076</t>
-  </si>
-  <si>
-    <t>0.1203,0.8809,0.0205,0.0030</t>
-  </si>
-  <si>
-    <t>0.0555,0.9343,0.0393,0.0014</t>
-  </si>
-  <si>
-    <t>0.1747,0.8609,0.0094,0.0033</t>
-  </si>
-  <si>
-    <t>0.4582,0.5615,0.0380,0.0064</t>
-  </si>
-  <si>
-    <t>0.0315,0.9665,0.0106,0.0012</t>
-  </si>
-  <si>
-    <t>0.0134,0.9769,0.0116,0.0028</t>
-  </si>
-  <si>
-    <t>0.4497,0.6061,0.0208,0.0038</t>
-  </si>
-  <si>
-    <t>0.5831,0.0598,0.3702,0.0584</t>
-  </si>
-  <si>
-    <t>0.1230,0.0470,0.8794,0.0063</t>
-  </si>
-  <si>
-    <t>0.3144,0.3176,0.3462,0.1933</t>
-  </si>
-  <si>
-    <t>0.6161,0.0575,0.3788,0.0270</t>
-  </si>
-  <si>
-    <t>0.0699,0.3065,0.0691,0.8919</t>
-  </si>
-  <si>
-    <t>0.0074,0.9798,0.0360,0.0033</t>
-  </si>
-  <si>
-    <t>0.0090,0.9661,0.0229,0.0251</t>
-  </si>
-  <si>
-    <t>0.0252,0.9128,0.0130,0.1495</t>
-  </si>
-  <si>
-    <t>0.0009,0.9944,0.0197,0.0016</t>
-  </si>
-  <si>
-    <t>0.0161,0.9510,0.1599,0.0029</t>
-  </si>
-  <si>
-    <t>0.4055,0.6322,0.0333,0.0028</t>
-  </si>
-  <si>
-    <t>0.2926,0.7474,0.0159,0.0047</t>
-  </si>
-  <si>
-    <t>0.9810,0.0090,0.0036,0.0047</t>
-  </si>
-  <si>
-    <t>0.9681,0.0156,0.0041,0.0089</t>
-  </si>
-  <si>
-    <t>0.9833,0.0032,0.0011,0.0076</t>
-  </si>
-  <si>
-    <t>0.9810,0.0038,0.0016,0.0071</t>
-  </si>
-  <si>
-    <t>0.9886,0.0024,0.0005,0.0050</t>
-  </si>
-  <si>
-    <t>0.9730,0.0175,0.0024,0.0044</t>
-  </si>
-  <si>
-    <t>0.9839,0.0027,0.0008,0.0074</t>
-  </si>
-  <si>
-    <t>0.9827,0.0062,0.0015,0.0041</t>
-  </si>
-  <si>
-    <t>0.0027,0.9082,0.7696,0.0007</t>
-  </si>
-  <si>
-    <t>0.0110,0.6440,0.8183,0.0025</t>
-  </si>
-  <si>
-    <t>0.0015,0.0204,0.9920,0.0032</t>
-  </si>
-  <si>
-    <t>0.0068,0.2617,0.9600,0.0007</t>
-  </si>
-  <si>
-    <t>0.1997,0.2808,0.0151,0.6787</t>
-  </si>
-  <si>
-    <t>0.5597,0.0809,0.0658,0.3342</t>
-  </si>
-  <si>
-    <t>0.5145,0.0104,0.6116,0.0063</t>
-  </si>
-  <si>
-    <t>0.6794,0.1191,0.1999,0.0559</t>
-  </si>
-  <si>
-    <t>0.0107,0.0050,0.0045,0.9921</t>
-  </si>
-  <si>
-    <t>0.0002,0.0004,0.0020,0.9993</t>
-  </si>
-  <si>
-    <t>0.0017,0.1649,0.0016,0.9944</t>
-  </si>
-  <si>
-    <t>0.0075,0.0018,0.0045,0.9937</t>
-  </si>
-  <si>
-    <t>0.0039,0.8595,0.7745,0.0029</t>
-  </si>
-  <si>
-    <t>0.9534,0.0043,0.0018,0.0355</t>
-  </si>
-  <si>
-    <t>0.6925,0.2882,0.0568,0.0097</t>
-  </si>
-  <si>
-    <t>0.9760,0.0029,0.0004,0.0134</t>
-  </si>
-  <si>
-    <t>0.4667,0.5499,0.0348,0.0052</t>
-  </si>
-  <si>
-    <t>0.9776,0.0037,0.0022,0.0100</t>
-  </si>
-  <si>
-    <t>0.6550,0.0477,0.0590,0.2338</t>
-  </si>
-  <si>
-    <t>0.8865,0.0012,0.0008,0.1638</t>
-  </si>
-  <si>
-    <t>0.0052,0.0379,0.9730,0.0123</t>
-  </si>
-  <si>
-    <t>0.4387,0.0026,0.0063,0.6712</t>
-  </si>
-  <si>
-    <t>0.7476,0.0016,0.0036,0.3334</t>
-  </si>
-  <si>
-    <t>0.6877,0.0966,0.2581,0.0385</t>
-  </si>
-  <si>
-    <t>0.8650,0.0439,0.0692,0.0190</t>
-  </si>
-  <si>
-    <t>0.8729,0.0891,0.0272,0.0166</t>
-  </si>
-  <si>
-    <t>0.6692,0.2627,0.0543,0.0418</t>
-  </si>
-  <si>
-    <t>0.4140,0.4715,0.1415,0.0088</t>
-  </si>
-  <si>
-    <t>0.5987,0.3828,0.0444,0.0257</t>
-  </si>
-  <si>
-    <t>0.9923,0.0011,0.0003,0.0038</t>
-  </si>
-  <si>
-    <t>0.9894,0.0025,0.0005,0.0040</t>
-  </si>
-  <si>
-    <t>0.9909,0.0016,0.0003,0.0041</t>
-  </si>
-  <si>
-    <t>0.9854,0.0007,0.0004,0.0145</t>
-  </si>
-  <si>
-    <t>0.9622,0.0184,0.0028,0.0104</t>
-  </si>
-  <si>
-    <t>0.9889,0.0029,0.0007,0.0037</t>
-  </si>
-  <si>
-    <t>0.9903,0.0033,0.0006,0.0025</t>
-  </si>
-  <si>
-    <t>0.9950,0.0008,0.0002,0.0021</t>
-  </si>
-  <si>
-    <t>0.2403,0.7904,0.0285,0.0050</t>
-  </si>
-  <si>
-    <t>0.7102,0.3599,0.0119,0.0038</t>
-  </si>
-  <si>
-    <t>0.2725,0.7104,0.0462,0.0046</t>
-  </si>
-  <si>
-    <t>0.7521,0.1659,0.0865,0.0738</t>
-  </si>
-  <si>
-    <t>0.9753,0.0227,0.0012,0.0032</t>
-  </si>
-  <si>
-    <t>0.9199,0.0758,0.0107,0.0083</t>
-  </si>
-  <si>
-    <t>0.9792,0.0169,0.0015,0.0025</t>
-  </si>
-  <si>
-    <t>0.7589,0.2554,0.0435,0.0126</t>
-  </si>
-  <si>
-    <t>0.0032,0.0289,0.9943,0.0005</t>
-  </si>
-  <si>
-    <t>0.9386,0.0346,0.0215,0.0124</t>
-  </si>
-  <si>
-    <t>0.0016,0.0018,0.9964,0.0014</t>
-  </si>
-  <si>
-    <t>0.0008,0.0190,0.9944,0.0020</t>
-  </si>
-  <si>
-    <t>0.0488,0.0155,0.9562,0.0029</t>
-  </si>
-  <si>
-    <t>0.0053,0.1159,0.9624,0.0077</t>
-  </si>
-  <si>
-    <t>0.0087,0.0173,0.9883,0.0012</t>
-  </si>
-  <si>
-    <t>0.0012,0.0009,0.9979,0.0009</t>
-  </si>
-  <si>
-    <t>0.0056,0.0110,0.9857,0.0053</t>
-  </si>
-  <si>
-    <t>0.5417,0.1944,0.2864,0.0132</t>
-  </si>
-  <si>
-    <t>0.2536,0.0484,0.7851,0.0067</t>
-  </si>
-  <si>
-    <t>0.5874,0.0497,0.3514,0.0639</t>
-  </si>
-  <si>
-    <t>0.2103,0.0969,0.7249,0.0074</t>
-  </si>
-  <si>
-    <t>0.3776,0.1119,0.5455,0.0071</t>
-  </si>
-  <si>
-    <t>0.1867,0.7093,0.0912,0.0528</t>
-  </si>
-  <si>
-    <t>0.6311,0.0915,0.2774,0.1196</t>
-  </si>
-  <si>
-    <t>0.3983,0.0475,0.6282,0.0260</t>
-  </si>
-  <si>
-    <t>0.7955,0.2385,0.0196,0.0064</t>
-  </si>
-  <si>
-    <t>0.7015,0.4186,0.0062,0.0025</t>
-  </si>
-  <si>
-    <t>0.8463,0.1613,0.0359,0.0151</t>
-  </si>
-  <si>
-    <t>0.9448,0.0331,0.0047,0.0141</t>
-  </si>
-  <si>
-    <t>0.8108,0.2343,0.0122,0.0080</t>
-  </si>
-  <si>
-    <t>0.3650,0.5569,0.1363,0.0667</t>
-  </si>
-  <si>
-    <t>0.7966,0.0199,0.1684,0.0155</t>
-  </si>
-  <si>
-    <t>0.4002,0.1073,0.1586,0.4597</t>
-  </si>
-  <si>
-    <t>0.7024,0.0465,0.1855,0.0689</t>
-  </si>
-  <si>
-    <t>0.6506,0.0392,0.3436,0.0133</t>
-  </si>
-  <si>
-    <t>0.0090,0.0060,0.9774,0.0176</t>
-  </si>
-  <si>
-    <t>0.0699,0.0477,0.9009,0.0114</t>
-  </si>
-  <si>
-    <t>0.0091,0.1275,0.9744,0.0009</t>
-  </si>
-  <si>
-    <t>0.0095,0.0695,0.9612,0.0117</t>
-  </si>
-  <si>
-    <t>0.0149,0.3325,0.9198,0.0043</t>
-  </si>
-  <si>
-    <t>0.9895,0.0004,0.0001,0.0104</t>
-  </si>
-  <si>
-    <t>0.9782,0.0193,0.0021,0.0030</t>
-  </si>
-  <si>
-    <t>0.9868,0.0064,0.0012,0.0031</t>
-  </si>
-  <si>
-    <t>0.9925,0.0021,0.0002,0.0024</t>
-  </si>
-  <si>
-    <t>0.9782,0.0046,0.0014,0.0112</t>
-  </si>
-  <si>
-    <t>0.9905,0.0014,0.0001,0.0046</t>
-  </si>
-  <si>
-    <t>0.9928,0.0013,0.0003,0.0033</t>
-  </si>
-  <si>
-    <t>0.9950,0.0012,0.0002,0.0017</t>
-  </si>
-  <si>
-    <t>0.0932,0.0053,0.9242,0.0098</t>
-  </si>
-  <si>
-    <t>0.6518,0.0704,0.3546,0.0167</t>
-  </si>
-  <si>
-    <t>0.9142,0.0130,0.0338,0.0208</t>
-  </si>
-  <si>
-    <t>0.0009,0.0118,0.9977,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0075,0.9988,0.0004</t>
-  </si>
-  <si>
-    <t>0.0262,0.0172,0.9658,0.0035</t>
-  </si>
-  <si>
-    <t>0.0005,0.0058,0.9976,0.0011</t>
-  </si>
-  <si>
-    <t>0.0665,0.0094,0.9297,0.0148</t>
-  </si>
-  <si>
-    <t>0.0017,0.0091,0.9942,0.0037</t>
-  </si>
-  <si>
-    <t>0.0130,0.0077,0.9695,0.0143</t>
-  </si>
-  <si>
-    <t>0.1098,0.0682,0.8666,0.0122</t>
-  </si>
-  <si>
-    <t>0.5201,0.0531,0.4544,0.0590</t>
-  </si>
-  <si>
-    <t>0.3683,0.0102,0.6970,0.0108</t>
-  </si>
-  <si>
-    <t>0.6960,0.0116,0.1104,0.1064</t>
-  </si>
-  <si>
-    <t>0.9873,0.0062,0.0010,0.0039</t>
-  </si>
-  <si>
-    <t>0.9909,0.0048,0.0006,0.0019</t>
-  </si>
-  <si>
-    <t>0.9924,0.0024,0.0005,0.0021</t>
-  </si>
-  <si>
-    <t>0.9874,0.0079,0.0013,0.0021</t>
-  </si>
-  <si>
-    <t>0.9941,0.0011,0.0001,0.0025</t>
-  </si>
-  <si>
-    <t>0.9860,0.0066,0.0016,0.0033</t>
-  </si>
-  <si>
-    <t>0.9935,0.0027,0.0002,0.0018</t>
-  </si>
-  <si>
-    <t>0.9883,0.0028,0.0004,0.0047</t>
-  </si>
-  <si>
-    <t>0.1169,0.1021,0.8208,0.0078</t>
-  </si>
-  <si>
-    <t>0.0041,0.0319,0.9877,0.0019</t>
-  </si>
-  <si>
-    <t>0.0075,0.1306,0.9702,0.0049</t>
-  </si>
-  <si>
-    <t>0.1287,0.2841,0.5646,0.0054</t>
-  </si>
-  <si>
-    <t>0.0105,0.0043,0.9800,0.0067</t>
-  </si>
-  <si>
-    <t>0.1225,0.0134,0.8732,0.0263</t>
-  </si>
-  <si>
-    <t>0.2518,0.0929,0.7076,0.0342</t>
-  </si>
-  <si>
-    <t>0.0330,0.1998,0.8903,0.0181</t>
-  </si>
-  <si>
-    <t>0.9215,0.0013,0.0018,0.0900</t>
-  </si>
-  <si>
-    <t>0.0214,0.0452,0.0048,0.9829</t>
-  </si>
-  <si>
-    <t>0.0100,0.0029,0.0022,0.9941</t>
-  </si>
-  <si>
-    <t>0.0017,0.0013,0.0008,0.9987</t>
-  </si>
-  <si>
-    <t>0.0012,0.0025,0.0008,0.9988</t>
-  </si>
-  <si>
-    <t>0.4410,0.0601,0.0512,0.5424</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.7726,0.0073,0.0251,0.1556</t>
+  </si>
+  <si>
+    <t>0.0066,0.0020,0.0061,0.9932</t>
+  </si>
+  <si>
+    <t>0.3483,0.0339,0.0101,0.6873</t>
+  </si>
+  <si>
+    <t>0.0477,0.0120,0.0172,0.9668</t>
+  </si>
+  <si>
+    <t>0.9952,0.0007,0.0001,0.0026</t>
+  </si>
+  <si>
+    <t>0.9945,0.0009,0.0002,0.0028</t>
+  </si>
+  <si>
+    <t>0.9903,0.0023,0.0005,0.0038</t>
+  </si>
+  <si>
+    <t>0.9935,0.0024,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.9900,0.0037,0.0005,0.0030</t>
+  </si>
+  <si>
+    <t>0.9952,0.0020,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9956,0.0009,0.0001,0.0016</t>
+  </si>
+  <si>
+    <t>0.9931,0.0018,0.0003,0.0030</t>
+  </si>
+  <si>
+    <t>0.6654,0.0728,0.2840,0.0354</t>
+  </si>
+  <si>
+    <t>0.1544,0.0394,0.8729,0.0048</t>
+  </si>
+  <si>
+    <t>0.1184,0.0259,0.9108,0.0033</t>
+  </si>
+  <si>
+    <t>0.1157,0.0217,0.8945,0.0041</t>
+  </si>
+  <si>
+    <t>0.5320,0.0244,0.4938,0.0366</t>
+  </si>
+  <si>
+    <t>0.0045,0.9865,0.0293,0.0020</t>
+  </si>
+  <si>
+    <t>0.0057,0.9885,0.0153,0.0005</t>
+  </si>
+  <si>
+    <t>0.1994,0.8261,0.0149,0.0040</t>
+  </si>
+  <si>
+    <t>0.0178,0.9729,0.0271,0.0011</t>
+  </si>
+  <si>
+    <t>0.0016,0.9954,0.0083,0.0004</t>
+  </si>
+  <si>
+    <t>0.2810,0.0105,0.7637,0.0232</t>
+  </si>
+  <si>
+    <t>0.2253,0.0060,0.8506,0.0038</t>
+  </si>
+  <si>
+    <t>0.0412,0.0050,0.9615,0.0069</t>
+  </si>
+  <si>
+    <t>0.2127,0.0150,0.7726,0.0498</t>
+  </si>
+  <si>
+    <t>0.0671,0.1008,0.8708,0.0143</t>
+  </si>
+  <si>
+    <t>0.0045,0.0024,0.9678,0.0795</t>
+  </si>
+  <si>
+    <t>0.0045,0.0023,0.9878,0.0076</t>
+  </si>
+  <si>
+    <t>0.2017,0.8139,0.0115,0.0081</t>
+  </si>
+  <si>
+    <t>0.3486,0.0930,0.6517,0.0057</t>
+  </si>
+  <si>
+    <t>0.0018,0.0074,0.9903,0.0102</t>
+  </si>
+  <si>
+    <t>0.0871,0.8820,0.0629,0.0054</t>
+  </si>
+  <si>
+    <t>0.8171,0.1703,0.0440,0.0156</t>
+  </si>
+  <si>
+    <t>0.7404,0.0943,0.1853,0.0289</t>
+  </si>
+  <si>
+    <t>0.8751,0.1745,0.0066,0.0028</t>
+  </si>
+  <si>
+    <t>0.0484,0.7805,0.4793,0.0093</t>
+  </si>
+  <si>
+    <t>0.0150,0.8441,0.3783,0.0225</t>
+  </si>
+  <si>
+    <t>0.0246,0.0422,0.9442,0.0212</t>
+  </si>
+  <si>
+    <t>0.0539,0.1780,0.8703,0.0200</t>
+  </si>
+  <si>
+    <t>0.0533,0.0110,0.8906,0.0577</t>
+  </si>
+  <si>
+    <t>0.0099,0.0194,0.9836,0.0020</t>
+  </si>
+  <si>
+    <t>0.0079,0.9562,0.1581,0.0038</t>
+  </si>
+  <si>
+    <t>0.0456,0.0230,0.9564,0.0020</t>
+  </si>
+  <si>
+    <t>0.0544,0.2344,0.0213,0.9401</t>
+  </si>
+  <si>
+    <t>0.0023,0.9868,0.0044,0.0201</t>
+  </si>
+  <si>
+    <t>0.0040,0.9868,0.0204,0.0032</t>
+  </si>
+  <si>
+    <t>0.0051,0.9791,0.0177,0.0133</t>
+  </si>
+  <si>
+    <t>0.0040,0.0672,0.9834,0.0034</t>
+  </si>
+  <si>
+    <t>0.0016,0.0712,0.9924,0.0010</t>
+  </si>
+  <si>
+    <t>0.2528,0.0665,0.6122,0.1551</t>
+  </si>
+  <si>
+    <t>0.0091,0.0019,0.9856,0.0061</t>
+  </si>
+  <si>
+    <t>0.0054,0.0100,0.9873,0.0043</t>
+  </si>
+  <si>
+    <t>0.0044,0.0091,0.9858,0.0069</t>
+  </si>
+  <si>
+    <t>0.9679,0.0256,0.0050,0.0048</t>
+  </si>
+  <si>
+    <t>0.9816,0.0077,0.0017,0.0062</t>
+  </si>
+  <si>
+    <t>0.9678,0.0146,0.0016,0.0077</t>
+  </si>
+  <si>
+    <t>0.0037,0.0254,0.9905,0.0020</t>
+  </si>
+  <si>
+    <t>0.9798,0.0038,0.0017,0.0114</t>
+  </si>
+  <si>
+    <t>0.9913,0.0020,0.0003,0.0039</t>
+  </si>
+  <si>
+    <t>0.9791,0.0103,0.0030,0.0058</t>
+  </si>
+  <si>
+    <t>0.0011,0.5553,0.9726,0.0011</t>
+  </si>
+  <si>
+    <t>0.0012,0.0134,0.9843,0.0173</t>
+  </si>
+  <si>
+    <t>0.0028,0.0266,0.9922,0.0012</t>
+  </si>
+  <si>
+    <t>0.0030,0.8482,0.8900,0.0007</t>
+  </si>
+  <si>
+    <t>0.0015,0.0056,0.9949,0.0029</t>
+  </si>
+  <si>
+    <t>0.0311,0.8565,0.3546,0.0025</t>
+  </si>
+  <si>
+    <t>0.0033,0.9910,0.0070,0.0011</t>
+  </si>
+  <si>
+    <t>0.0719,0.0252,0.9320,0.0115</t>
+  </si>
+  <si>
+    <t>0.0774,0.3261,0.7940,0.0063</t>
+  </si>
+  <si>
+    <t>0.0042,0.0309,0.9909,0.0009</t>
+  </si>
+  <si>
+    <t>0.0051,0.7931,0.8422,0.0013</t>
+  </si>
+  <si>
+    <t>0.0126,0.6790,0.7929,0.0023</t>
+  </si>
+  <si>
+    <t>0.0027,0.9620,0.3774,0.0033</t>
+  </si>
+  <si>
+    <t>0.0071,0.7595,0.8623,0.0035</t>
+  </si>
+  <si>
+    <t>0.0079,0.0014,0.0121,0.9893</t>
+  </si>
+  <si>
+    <t>0.0057,0.0036,0.0013,0.9964</t>
+  </si>
+  <si>
+    <t>0.0020,0.0041,0.0028,0.9973</t>
+  </si>
+  <si>
+    <t>0.0030,0.0118,0.0020,0.9967</t>
+  </si>
+  <si>
+    <t>0.0148,0.0064,0.0024,0.9913</t>
+  </si>
+  <si>
+    <t>0.0125,0.0065,0.0043,0.9913</t>
+  </si>
+  <si>
+    <t>0.0024,0.8631,0.8969,0.0007</t>
+  </si>
+  <si>
+    <t>0.0014,0.8631,0.9370,0.0004</t>
+  </si>
+  <si>
+    <t>0.0092,0.8156,0.6969,0.0040</t>
+  </si>
+  <si>
+    <t>0.0162,0.0958,0.9541,0.0076</t>
+  </si>
+  <si>
+    <t>0.0005,0.9728,0.7255,0.0001</t>
+  </si>
+  <si>
+    <t>0.0120,0.7494,0.7178,0.0092</t>
+  </si>
+  <si>
+    <t>0.9940,0.0014,0.0002,0.0023</t>
+  </si>
+  <si>
+    <t>0.9755,0.0124,0.0016,0.0065</t>
+  </si>
+  <si>
+    <t>0.9888,0.0064,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9912,0.0024,0.0005,0.0037</t>
+  </si>
+  <si>
+    <t>0.9881,0.0022,0.0007,0.0056</t>
+  </si>
+  <si>
+    <t>0.9935,0.0017,0.0003,0.0022</t>
+  </si>
+  <si>
+    <t>0.9908,0.0034,0.0007,0.0028</t>
+  </si>
+  <si>
+    <t>0.9906,0.0040,0.0008,0.0025</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0001,0.0014</t>
+  </si>
+  <si>
+    <t>0.9916,0.0009,0.0002,0.0046</t>
+  </si>
+  <si>
+    <t>0.9905,0.0014,0.0002,0.0049</t>
+  </si>
+  <si>
+    <t>0.9931,0.0010,0.0002,0.0038</t>
+  </si>
+  <si>
+    <t>0.9875,0.0060,0.0009,0.0036</t>
+  </si>
+  <si>
+    <t>0.9936,0.0024,0.0005,0.0016</t>
+  </si>
+  <si>
+    <t>0.9956,0.0005,0.0001,0.0023</t>
+  </si>
+  <si>
+    <t>0.9969,0.0005,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.0018,0.0010,0.9895,0.0205</t>
+  </si>
+  <si>
+    <t>0.0311,0.0169,0.9576,0.0086</t>
+  </si>
+  <si>
+    <t>0.4636,0.0879,0.4650,0.1375</t>
+  </si>
+  <si>
+    <t>0.0204,0.0032,0.9706,0.0127</t>
+  </si>
+  <si>
+    <t>0.0509,0.9458,0.0190,0.0012</t>
+  </si>
+  <si>
+    <t>0.0645,0.9272,0.0382,0.0034</t>
+  </si>
+  <si>
+    <t>0.0837,0.9185,0.0194,0.0022</t>
+  </si>
+  <si>
+    <t>0.3082,0.7538,0.0158,0.0028</t>
+  </si>
+  <si>
+    <t>0.0824,0.9147,0.0204,0.0056</t>
+  </si>
+  <si>
+    <t>0.0081,0.9849,0.0139,0.0011</t>
+  </si>
+  <si>
+    <t>0.7508,0.3256,0.0141,0.0029</t>
+  </si>
+  <si>
+    <t>0.5253,0.1042,0.3981,0.1113</t>
+  </si>
+  <si>
+    <t>0.1752,0.0645,0.8044,0.0031</t>
+  </si>
+  <si>
+    <t>0.4126,0.4276,0.1259,0.1760</t>
+  </si>
+  <si>
+    <t>0.0606,0.2324,0.8186,0.0050</t>
+  </si>
+  <si>
+    <t>0.1568,0.1480,0.0231,0.8565</t>
+  </si>
+  <si>
+    <t>0.0013,0.9926,0.0103,0.0052</t>
+  </si>
+  <si>
+    <t>0.0035,0.9860,0.0101,0.0088</t>
+  </si>
+  <si>
+    <t>0.0426,0.8689,0.0588,0.1787</t>
+  </si>
+  <si>
+    <t>0.0006,0.9879,0.2464,0.0006</t>
+  </si>
+  <si>
+    <t>0.0100,0.9746,0.0839,0.0009</t>
+  </si>
+  <si>
+    <t>0.7547,0.2808,0.0199,0.0092</t>
+  </si>
+  <si>
+    <t>0.8480,0.1963,0.0102,0.0038</t>
+  </si>
+  <si>
+    <t>0.9338,0.0674,0.0084,0.0070</t>
+  </si>
+  <si>
+    <t>0.9892,0.0042,0.0006,0.0028</t>
+  </si>
+  <si>
+    <t>0.9755,0.0050,0.0012,0.0134</t>
+  </si>
+  <si>
+    <t>0.9810,0.0036,0.0016,0.0069</t>
+  </si>
+  <si>
+    <t>0.9937,0.0012,0.0003,0.0026</t>
+  </si>
+  <si>
+    <t>0.9624,0.0289,0.0137,0.0038</t>
+  </si>
+  <si>
+    <t>0.9794,0.0057,0.0009,0.0077</t>
+  </si>
+  <si>
+    <t>0.9853,0.0004,0.0001,0.0164</t>
+  </si>
+  <si>
+    <t>0.0012,0.6282,0.9732,0.0001</t>
+  </si>
+  <si>
+    <t>0.0165,0.7666,0.6662,0.0049</t>
+  </si>
+  <si>
+    <t>0.0012,0.0842,0.9917,0.0008</t>
+  </si>
+  <si>
+    <t>0.0573,0.2958,0.8448,0.0142</t>
+  </si>
+  <si>
+    <t>0.6334,0.1015,0.3082,0.0924</t>
+  </si>
+  <si>
+    <t>0.7594,0.0537,0.1667,0.0374</t>
+  </si>
+  <si>
+    <t>0.3449,0.0063,0.7074,0.0162</t>
+  </si>
+  <si>
+    <t>0.7379,0.0494,0.2230,0.0218</t>
+  </si>
+  <si>
+    <t>0.0044,0.0018,0.0035,0.9956</t>
+  </si>
+  <si>
+    <t>0.0030,0.0018,0.0076,0.9949</t>
+  </si>
+  <si>
+    <t>0.0023,0.0147,0.0042,0.9961</t>
+  </si>
+  <si>
+    <t>0.0033,0.0017,0.0012,0.9975</t>
+  </si>
+  <si>
+    <t>0.0023,0.6010,0.9512,0.0009</t>
+  </si>
+  <si>
+    <t>0.9819,0.0046,0.0009,0.0076</t>
+  </si>
+  <si>
+    <t>0.5939,0.3875,0.0641,0.0134</t>
+  </si>
+  <si>
+    <t>0.9905,0.0028,0.0007,0.0032</t>
+  </si>
+  <si>
+    <t>0.5982,0.3658,0.0762,0.0075</t>
+  </si>
+  <si>
+    <t>0.9587,0.0147,0.0077,0.0111</t>
+  </si>
+  <si>
+    <t>0.7202,0.0041,0.0125,0.2886</t>
+  </si>
+  <si>
+    <t>0.9742,0.0023,0.0006,0.0179</t>
+  </si>
+  <si>
+    <t>0.0082,0.0809,0.9528,0.0177</t>
+  </si>
+  <si>
+    <t>0.7737,0.0020,0.0571,0.0732</t>
+  </si>
+  <si>
+    <t>0.6089,0.0083,0.0078,0.4265</t>
+  </si>
+  <si>
+    <t>0.1520,0.8163,0.0709,0.0104</t>
+  </si>
+  <si>
+    <t>0.7666,0.1433,0.0778,0.0609</t>
+  </si>
+  <si>
+    <t>0.7971,0.1260,0.0744,0.0431</t>
+  </si>
+  <si>
+    <t>0.5333,0.1680,0.3538,0.0337</t>
+  </si>
+  <si>
+    <t>0.4642,0.4375,0.1644,0.0197</t>
+  </si>
+  <si>
+    <t>0.5349,0.4659,0.0523,0.0086</t>
+  </si>
+  <si>
+    <t>0.9897,0.0036,0.0007,0.0026</t>
+  </si>
+  <si>
+    <t>0.9913,0.0021,0.0003,0.0034</t>
+  </si>
+  <si>
+    <t>0.9938,0.0011,0.0003,0.0023</t>
+  </si>
+  <si>
+    <t>0.9857,0.0012,0.0004,0.0093</t>
+  </si>
+  <si>
+    <t>0.9808,0.0035,0.0005,0.0095</t>
+  </si>
+  <si>
+    <t>0.9653,0.0122,0.0027,0.0094</t>
+  </si>
+  <si>
+    <t>0.9921,0.0009,0.0002,0.0046</t>
+  </si>
+  <si>
+    <t>0.9928,0.0018,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.4918,0.5856,0.0227,0.0033</t>
+  </si>
+  <si>
+    <t>0.5479,0.5386,0.0156,0.0034</t>
+  </si>
+  <si>
+    <t>0.3279,0.7090,0.0148,0.0032</t>
+  </si>
+  <si>
+    <t>0.1448,0.4761,0.5821,0.0130</t>
+  </si>
+  <si>
+    <t>0.9752,0.0120,0.0022,0.0060</t>
+  </si>
+  <si>
+    <t>0.9498,0.0402,0.0077,0.0089</t>
+  </si>
+  <si>
+    <t>0.9675,0.0197,0.0018,0.0066</t>
+  </si>
+  <si>
+    <t>0.8994,0.1218,0.0060,0.0065</t>
+  </si>
+  <si>
+    <t>0.0030,0.0131,0.9929,0.0022</t>
+  </si>
+  <si>
+    <t>0.9529,0.0470,0.0123,0.0035</t>
+  </si>
+  <si>
+    <t>0.0013,0.0036,0.9973,0.0006</t>
+  </si>
+  <si>
+    <t>0.0236,0.0527,0.9525,0.0114</t>
+  </si>
+  <si>
+    <t>0.0232,0.0095,0.9745,0.0024</t>
+  </si>
+  <si>
+    <t>0.0077,0.0354,0.9771,0.0062</t>
+  </si>
+  <si>
+    <t>0.0195,0.0146,0.9799,0.0011</t>
+  </si>
+  <si>
+    <t>0.0076,0.0029,0.9909,0.0023</t>
+  </si>
+  <si>
+    <t>0.0041,0.0079,0.9905,0.0034</t>
+  </si>
+  <si>
+    <t>0.6490,0.0343,0.3788,0.0143</t>
+  </si>
+  <si>
+    <t>0.1072,0.0127,0.9217,0.0047</t>
+  </si>
+  <si>
+    <t>0.6751,0.2130,0.1296,0.0346</t>
+  </si>
+  <si>
+    <t>0.5544,0.1334,0.3769,0.0177</t>
+  </si>
+  <si>
+    <t>0.2935,0.0803,0.6668,0.0088</t>
+  </si>
+  <si>
+    <t>0.3867,0.0965,0.5708,0.0218</t>
+  </si>
+  <si>
+    <t>0.7992,0.0859,0.0411,0.0422</t>
+  </si>
+  <si>
+    <t>0.5017,0.0385,0.5262,0.0312</t>
+  </si>
+  <si>
+    <t>0.2002,0.8261,0.0203,0.0021</t>
+  </si>
+  <si>
+    <t>0.7867,0.3002,0.0099,0.0026</t>
+  </si>
+  <si>
+    <t>0.6333,0.3900,0.0354,0.0106</t>
+  </si>
+  <si>
+    <t>0.9868,0.0070,0.0010,0.0031</t>
+  </si>
+  <si>
+    <t>0.9829,0.0091,0.0009,0.0043</t>
+  </si>
+  <si>
+    <t>0.4948,0.3253,0.2052,0.0830</t>
+  </si>
+  <si>
+    <t>0.4610,0.0089,0.6465,0.0134</t>
+  </si>
+  <si>
+    <t>0.0866,0.0777,0.0270,0.9236</t>
+  </si>
+  <si>
+    <t>0.2131,0.0073,0.6385,0.1274</t>
+  </si>
+  <si>
+    <t>0.4447,0.0417,0.0751,0.5230</t>
+  </si>
+  <si>
+    <t>0.0036,0.0047,0.9859,0.0149</t>
+  </si>
+  <si>
+    <t>0.0577,0.0984,0.8685,0.0415</t>
+  </si>
+  <si>
+    <t>0.0115,0.0119,0.9824,0.0028</t>
+  </si>
+  <si>
+    <t>0.0107,0.0194,0.9812,0.0033</t>
+  </si>
+  <si>
+    <t>0.0189,0.3134,0.9091,0.0081</t>
+  </si>
+  <si>
+    <t>0.9904,0.0038,0.0004,0.0028</t>
+  </si>
+  <si>
+    <t>0.9866,0.0054,0.0014,0.0039</t>
+  </si>
+  <si>
+    <t>0.9858,0.0031,0.0004,0.0062</t>
+  </si>
+  <si>
+    <t>0.9906,0.0048,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.9820,0.0095,0.0021,0.0048</t>
+  </si>
+  <si>
+    <t>0.9884,0.0030,0.0009,0.0037</t>
+  </si>
+  <si>
+    <t>0.9937,0.0010,0.0002,0.0030</t>
+  </si>
+  <si>
+    <t>0.9907,0.0011,0.0004,0.0050</t>
+  </si>
+  <si>
+    <t>0.3999,0.0669,0.6330,0.0225</t>
+  </si>
+  <si>
+    <t>0.2719,0.1441,0.6813,0.0076</t>
+  </si>
+  <si>
+    <t>0.9514,0.0091,0.0129,0.0135</t>
+  </si>
+  <si>
+    <t>0.0024,0.0224,0.9938,0.0008</t>
+  </si>
+  <si>
+    <t>0.0007,0.0086,0.9975,0.0008</t>
+  </si>
+  <si>
+    <t>0.0579,0.1029,0.8679,0.0070</t>
+  </si>
+  <si>
+    <t>0.0021,0.0078,0.9954,0.0012</t>
+  </si>
+  <si>
+    <t>0.0533,0.0301,0.9230,0.0173</t>
+  </si>
+  <si>
+    <t>0.0002,0.0038,0.9986,0.0006</t>
+  </si>
+  <si>
+    <t>0.0121,0.0168,0.9760,0.0054</t>
+  </si>
+  <si>
+    <t>0.1787,0.2139,0.7271,0.0349</t>
+  </si>
+  <si>
+    <t>0.5711,0.0104,0.2994,0.0582</t>
+  </si>
+  <si>
+    <t>0.2233,0.0086,0.6891,0.1022</t>
+  </si>
+  <si>
+    <t>0.5115,0.0406,0.2086,0.2620</t>
+  </si>
+  <si>
+    <t>0.9887,0.0018,0.0002,0.0056</t>
+  </si>
+  <si>
+    <t>0.9779,0.0129,0.0030,0.0050</t>
+  </si>
+  <si>
+    <t>0.9907,0.0032,0.0006,0.0032</t>
+  </si>
+  <si>
+    <t>0.9892,0.0041,0.0006,0.0029</t>
+  </si>
+  <si>
+    <t>0.9827,0.0051,0.0009,0.0072</t>
+  </si>
+  <si>
+    <t>0.9937,0.0024,0.0003,0.0018</t>
+  </si>
+  <si>
+    <t>0.9961,0.0013,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9869,0.0040,0.0009,0.0042</t>
+  </si>
+  <si>
+    <t>0.0591,0.0373,0.9297,0.0054</t>
+  </si>
+  <si>
+    <t>0.0093,0.0310,0.9767,0.0057</t>
+  </si>
+  <si>
+    <t>0.0010,0.1185,0.9903,0.0011</t>
+  </si>
+  <si>
+    <t>0.1395,0.0162,0.8537,0.0202</t>
+  </si>
+  <si>
+    <t>0.0117,0.0329,0.9696,0.0087</t>
+  </si>
+  <si>
+    <t>0.1618,0.0039,0.3340,0.3874</t>
+  </si>
+  <si>
+    <t>0.4053,0.0325,0.5510,0.0572</t>
+  </si>
+  <si>
+    <t>0.0130,0.0412,0.9674,0.0096</t>
+  </si>
+  <si>
+    <t>0.5438,0.0088,0.0484,0.4497</t>
+  </si>
+  <si>
+    <t>0.0046,0.0273,0.0089,0.9921</t>
+  </si>
+  <si>
+    <t>0.0151,0.0144,0.0158,0.9838</t>
+  </si>
+  <si>
+    <t>0.0016,0.0029,0.0007,0.9986</t>
+  </si>
+  <si>
+    <t>0.0026,0.0015,0.0024,0.9971</t>
+  </si>
+  <si>
+    <t>0.7937,0.0455,0.0319,0.1048</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1993,7 @@
         <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2133,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2231,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,7 +2385,7 @@
         <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2438,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2455,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,7 +2483,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2648,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2973,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2984,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3110,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3141,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,7 +3169,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,10 +3432,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3505,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3586,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3617,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3841,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3855,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3869,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,10 +3894,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4037,7 @@
         <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4062,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,10 +4216,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4370,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4387,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4591,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4625,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4636,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4675,7 +4681,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4692,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,10 +4706,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,10 +4790,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4804,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4818,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4832,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4877,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5406,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5451,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,10 +5518,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
